--- a/data/trans_orig/Q5405-Edad-trans_orig.xlsx
+++ b/data/trans_orig/Q5405-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>839</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11443</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11025</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3800</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16303</t>
+          <t>16244</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1729</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3624</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14109</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6511</t>
+          <t>6578</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20502</t>
+          <t>19629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>276195</t>
+          <t>277109</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>288876</t>
+          <t>289001</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>322310</t>
+          <t>322930</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>336109</t>
+          <t>335653</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>605015</t>
+          <t>605069</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>622596</t>
+          <t>622574</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>941</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9361</t>
+          <t>9278</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26128</t>
+          <t>24579</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>10315</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>28953</t>
+          <t>27995</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8879</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22869</t>
+          <t>23491</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>5449</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>19848</t>
+          <t>18985</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16267</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182976</t>
+          <t>183115</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198322</t>
+          <t>198047</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>298088</t>
+          <t>295791</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>317903</t>
+          <t>317338</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>486436</t>
+          <t>487537</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>513173</t>
+          <t>512467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>2867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15269</t>
+          <t>14412</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11881</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30120</t>
+          <t>29993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>17292</t>
+          <t>17891</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>39384</t>
+          <t>39753</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>12484</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28255</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10793</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28575</t>
+          <t>27269</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>26524</t>
+          <t>26258</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>50437</t>
+          <t>50270</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>465631</t>
+          <t>464648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>484742</t>
+          <t>484327</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>626134</t>
+          <t>627579</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>650983</t>
+          <t>650948</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1099217</t>
+          <t>1099327</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1128971</t>
+          <t>1130302</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -2331,12 +2331,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>985</t>
+          <t>981</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>8890</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8010</t>
+          <t>7885</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>13271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2416,12 +2416,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4141</t>
+          <t>4066</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18163</t>
+          <t>19083</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2479,12 +2479,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5764</t>
+          <t>5776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18369</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,7 +2499,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>11976</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>29859</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2529,12 +2529,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>287724</t>
+          <t>287269</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>303548</t>
+          <t>303562</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>332611</t>
+          <t>332474</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>347057</t>
+          <t>346239</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>625642</t>
+          <t>626651</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>646418</t>
+          <t>646500</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2787,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>9522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25708</t>
+          <t>25355</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2802,12 +2802,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>18666</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40353</t>
+          <t>42343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2837,12 +2837,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32353</t>
+          <t>32418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61042</t>
+          <t>60356</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2872,12 +2872,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>17984</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>41286</t>
+          <t>40075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23647</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46577</t>
+          <t>47608</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2950,12 +2950,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>46512</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>81291</t>
+          <t>78767</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,33%</t>
         </is>
       </c>
     </row>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>191898</t>
+          <t>192725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>218322</t>
+          <t>218626</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3028,12 +3028,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>307995</t>
+          <t>308498</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>339558</t>
+          <t>339473</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>509924</t>
+          <t>510179</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>549986</t>
+          <t>550586</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,19%</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11646</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29849</t>
+          <t>28999</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3258,12 +3258,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21333</t>
+          <t>21395</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>43281</t>
+          <t>43463</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3293,12 +3293,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>37460</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>67782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -3356,12 +3356,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>52936</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>34045</t>
+          <t>33010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60469</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3406,12 +3406,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>64038</t>
+          <t>63989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102167</t>
+          <t>101298</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3441,12 +3441,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -3469,12 +3469,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>486521</t>
+          <t>486612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>517838</t>
+          <t>517510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3484,12 +3484,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>647417</t>
+          <t>648182</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>681466</t>
+          <t>681602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1146378</t>
+          <t>1146537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1192250</t>
+          <t>1191621</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,48%</t>
         </is>
       </c>
     </row>
@@ -3929,12 +3929,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>948</t>
+          <t>951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7837</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>7248</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1966</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>11487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4014,12 +4014,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7992</t>
+          <t>7704</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4077,12 +4077,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13166</t>
+          <t>13313</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4092,12 +4092,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4556</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18044</t>
+          <t>16921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4127,12 +4127,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -4155,12 +4155,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>322606</t>
+          <t>322429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>332271</t>
+          <t>332210</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4170,12 +4170,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>361644</t>
+          <t>361365</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>373931</t>
+          <t>373914</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4205,12 +4205,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>688097</t>
+          <t>689232</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704013</t>
+          <t>704154</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4240,12 +4240,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -4385,12 +4385,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3331</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6539</t>
+          <t>7216</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23779</t>
+          <t>24054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4435,12 +4435,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13222</t>
+          <t>12319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32268</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5047</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>17907</t>
+          <t>17363</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24793</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>49389</t>
+          <t>48348</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>32767</t>
+          <t>33706</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61697</t>
+          <t>61235</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4583,12 +4583,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>229457</t>
+          <t>230391</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>244910</t>
+          <t>245781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>337043</t>
+          <t>336804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>365586</t>
+          <t>364550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4661,12 +4661,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>572013</t>
+          <t>573838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>605227</t>
+          <t>605935</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4696,12 +4696,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -4841,12 +4841,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5947</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18011</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4856,12 +4856,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>8319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26625</t>
+          <t>25536</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4891,12 +4891,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15847</t>
+          <t>16789</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37506</t>
+          <t>38095</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4926,12 +4926,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -4954,12 +4954,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7665</t>
+          <t>7404</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4969,12 +4969,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>29236</t>
+          <t>29411</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56384</t>
+          <t>57116</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41115</t>
+          <t>42085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71242</t>
+          <t>72385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,29%</t>
         </is>
       </c>
     </row>
@@ -5067,12 +5067,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>558402</t>
+          <t>557263</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>575653</t>
+          <t>575894</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>702817</t>
+          <t>702674</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>734475</t>
+          <t>735218</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1270269</t>
+          <t>1270290</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1305511</t>
+          <t>1305082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5157,7 +5157,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,31%</t>
         </is>
       </c>
     </row>
@@ -5522,44 +5522,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>1986</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>458</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6409</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6201</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -5567,57 +5567,57 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2443</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6459</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2410</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>569</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6332</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,25%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -5635,32 +5635,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1893</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>466</t>
+          <t>480</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5811</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6836</t>
+          <t>7390</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2038</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>12149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5705,32 +5705,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9282</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>5444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>15407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -5748,32 +5748,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>364394</t>
+          <t>403202</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>359235</t>
+          <t>397872</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>366595</t>
+          <t>405262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>600681</t>
+          <t>430887</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>594022</t>
+          <t>426037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>605789</t>
+          <t>434208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5818,32 +5818,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>965076</t>
+          <t>834089</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>958174</t>
+          <t>827430</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>971093</t>
+          <t>838651</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -5861,17 +5861,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5896,17 +5896,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>607958</t>
+          <t>438734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5931,17 +5931,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>976124</t>
+          <t>845814</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5978,32 +5978,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4787</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2311</t>
+          <t>2251</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8728</t>
+          <t>9033</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6013,32 +6013,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23376</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>17708</t>
+          <t>17894</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31933</t>
+          <t>33613</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>28163</t>
+          <t>29739</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>21412</t>
+          <t>22093</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37413</t>
+          <t>38739</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -6091,32 +6091,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8602</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19470</t>
+          <t>21023</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6126,32 +6126,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>32850</t>
+          <t>35010</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>27193</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42557</t>
+          <t>44705</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6161,32 +6161,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>45807</t>
+          <t>48427</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>36022</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55491</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -6204,32 +6204,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>264269</t>
+          <t>291209</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>257309</t>
+          <t>283693</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>269764</t>
+          <t>297027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,24%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6239,32 +6239,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>368901</t>
+          <t>403643</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>356067</t>
+          <t>390824</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>378095</t>
+          <t>414207</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6274,32 +6274,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>633170</t>
+          <t>694851</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>620764</t>
+          <t>680568</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>645292</t>
+          <t>706931</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,45%</t>
         </is>
       </c>
     </row>
@@ -6317,17 +6317,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>282013</t>
+          <t>309312</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6352,17 +6352,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>425128</t>
+          <t>463705</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>425128</t>
+          <t>463705</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425128</t>
+          <t>463705</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6387,17 +6387,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>707141</t>
+          <t>773016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>707141</t>
+          <t>773016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>707141</t>
+          <t>773016</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6434,32 +6434,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3526</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11369</t>
+          <t>11582</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6469,32 +6469,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23818</t>
+          <t>25510</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12118</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32824</t>
+          <t>33615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6504,32 +6504,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>30573</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19598</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>40932</t>
+          <t>42261</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -6547,32 +6547,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15310</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>21135</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6582,32 +6582,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39686</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20465</t>
+          <t>33943</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53661</t>
+          <t>52749</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6617,32 +6617,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>54445</t>
+          <t>57709</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>35883</t>
+          <t>46680</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>67752</t>
+          <t>69330</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -6660,32 +6660,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>628664</t>
+          <t>694410</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>620766</t>
+          <t>685616</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>635141</t>
+          <t>700632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6695,32 +6695,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>969582</t>
+          <t>834530</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949625</t>
+          <t>821131</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1002534</t>
+          <t>845724</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6730,32 +6730,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1598246</t>
+          <t>1528940</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1580236</t>
+          <t>1514621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1625466</t>
+          <t>1542535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -6773,17 +6773,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6808,17 +6808,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1033086</t>
+          <t>902439</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6843,17 +6843,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1683264</t>
+          <t>1618830</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
